--- a/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260603.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260603.xlsx
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>47,467</t>
+          <t>46,834</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>12.31%</t>
+          <t>12.21%</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>125,690</t>
+          <t>124,014</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>11.24%</t>
+          <t>11.17%</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>82,307</t>
+          <t>81,210</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>9.19%</t>
+          <t>9.30%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>38,020</t>
+          <t>37,513</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.18%</t>
+          <t>7.30%</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>40,921</t>
+          <t>40,375</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.26%</t>
+          <t>5.32%</t>
         </is>
       </c>
     </row>
@@ -721,12 +721,12 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>56,222</t>
+          <t>55,473</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.55%</t>
+          <t>4.33%</t>
         </is>
       </c>
     </row>
@@ -743,12 +743,12 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>152,038</t>
+          <t>150,011</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.48%</t>
+          <t>3.45%</t>
         </is>
       </c>
     </row>
@@ -765,12 +765,12 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>75,277</t>
+          <t>74,273</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.06%</t>
+          <t>2.96%</t>
         </is>
       </c>
     </row>
@@ -787,12 +787,12 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>120,586</t>
+          <t>118,978</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.92%</t>
+          <t>2.93%</t>
         </is>
       </c>
     </row>
@@ -809,12 +809,12 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>34,011</t>
+          <t>33,558</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.83%</t>
+          <t>2.90%</t>
         </is>
       </c>
     </row>
@@ -831,7 +831,7 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>85,131</t>
+          <t>83,996</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -853,12 +853,12 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>124,653</t>
+          <t>122,991</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.22%</t>
+          <t>2.19%</t>
         </is>
       </c>
     </row>
@@ -875,7 +875,7 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>58,383</t>
+          <t>57,604</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -897,12 +897,12 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>10,233</t>
+          <t>10,097</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>1.81%</t>
+          <t>1.88%</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>21,745</t>
+          <t>21,455</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.74%</t>
+          <t>1.75%</t>
         </is>
       </c>
     </row>
@@ -941,7 +941,7 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>67,672</t>
+          <t>66,769</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -963,12 +963,12 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>15,506</t>
+          <t>15,299</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.52%</t>
+          <t>1.54%</t>
         </is>
       </c>
     </row>
@@ -985,7 +985,7 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>52,653</t>
+          <t>51,951</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>110,684</t>
+          <t>109,208</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.33%</t>
+          <t>1.34%</t>
         </is>
       </c>
     </row>
@@ -1029,29 +1029,29 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>18,671</t>
+          <t>18,422</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.19%</t>
+          <t>1.20%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>PEG US</t>
+          <t>GNRC US</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>大眾服務企業集團公司</t>
+          <t>基內瑞克控股公司</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>54,641</t>
+          <t>14,668</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -1063,61 +1063,61 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>GNRC US</t>
+          <t>PEG US</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>基內瑞克控股公司</t>
+          <t>大眾服務企業集團公司</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>14,866</t>
+          <t>53,912</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.13%</t>
+          <t>1.14%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>CEG US</t>
+          <t>EIX US</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>星座能源公司</t>
+          <t>愛迪生國際</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>14,807</t>
+          <t>55,417</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.08%</t>
+          <t>1.07%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>EIX US</t>
+          <t>CEG US</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>愛迪生國際</t>
+          <t>星座能源公司</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>56,166</t>
+          <t>14,609</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>35,602</t>
+          <t>35,127</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1161,29 +1161,29 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>11,641</t>
+          <t>11,485</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.04%</t>
+          <t>1.03%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>ES US</t>
+          <t>TTEK UW</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Eversource能源</t>
+          <t>德照科技公司</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>54,756</t>
+          <t>131,878</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1195,22 +1195,22 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>TTEK UW</t>
+          <t>ES US</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>德照科技公司</t>
+          <t>Eversource能源</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>133,660</t>
+          <t>54,026</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>1.00%</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>32,556</t>
+          <t>32,122</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>0.95%</t>
         </is>
       </c>
     </row>
@@ -1249,7 +1249,7 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>43,148</t>
+          <t>42,573</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>43,944</t>
+          <t>43,358</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>0.85%</t>
         </is>
       </c>
     </row>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>63,223</t>
+          <t>62,380</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1315,12 +1315,12 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>80,997</t>
+          <t>79,917</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>0.76%</t>
         </is>
       </c>
     </row>
@@ -1337,56 +1337,56 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>15,920</t>
+          <t>15,707</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.67%</t>
+          <t>0.66%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>ENPH US</t>
+          <t>202606ESM6</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>Enphase能源公司</t>
+          <t>小型S＆P 500股價指數</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>32,433</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.63%</t>
+          <t>0.62%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>202606ESM6</t>
+          <t>ENPH US</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>小型S＆P 500股價指數</t>
+          <t>Enphase能源公司</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>32,001</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.61%</t>
+          <t>0.60%</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>15,120</t>
+          <t>14,918</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>19,685</t>
+          <t>19,422</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>24,890</t>
+          <t>24,558</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>17,447</t>
+          <t>17,214</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.47%</t>
         </is>
       </c>
     </row>
@@ -1491,7 +1491,7 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>22,100</t>
+          <t>21,806</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>29,884</t>
+          <t>29,485</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -1525,17 +1525,17 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>LNT US</t>
+          <t>PCG US</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>聯合能源公司</t>
+          <t>太平洋電力瓦斯公司</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>18,741</t>
+          <t>78,832</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -1547,22 +1547,22 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>PCG US</t>
+          <t>LNT US</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>太平洋電力瓦斯公司</t>
+          <t>聯合能源公司</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>79,897</t>
+          <t>18,491</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>0.36%</t>
         </is>
       </c>
     </row>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>30,860</t>
+          <t>30,449</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>9,016</t>
+          <t>8,896</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -1613,17 +1613,17 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>AMSC US</t>
+          <t>AES US</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>美國超導公司</t>
+          <t>愛伊斯公司</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>22,401</t>
+          <t>76,648</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -1635,22 +1635,22 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>AES US</t>
+          <t>AMSC US</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>愛伊斯公司</t>
+          <t>美國超導公司</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>77,683</t>
+          <t>22,103</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.28%</t>
         </is>
       </c>
     </row>
@@ -1667,12 +1667,12 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>11,067</t>
+          <t>10,920</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>0.25%</t>
+          <t>0.24%</t>
         </is>
       </c>
     </row>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>34,594</t>
+          <t>34,132</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>51,453</t>
+          <t>50,767</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -1729,7 +1729,7 @@
       <c r="B72" s="3" t="inlineStr"/>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>134,613,960</t>
+          <t>139,549,464</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr"/>
